--- a/_ForDRA/BVSimulationFiles/75.xlsx
+++ b/_ForDRA/BVSimulationFiles/75.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.002173913043478261</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002122181051079939</v>
+        <v>0.04244362102159878</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002061264803224258</v>
+        <v>0.04122529606448516</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001993320395105952</v>
+        <v>0.03986640790211904</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001920182286218682</v>
+        <v>0.03840364572437364</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001843404479934556</v>
+        <v>0.03686808959869112</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001764296825192162</v>
+        <v>0.03528593650384324</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001683956991448237</v>
+        <v>0.03367913982896474</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001603298607719339</v>
+        <v>0.03206597215438678</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001523076002665711</v>
+        <v>0.03046152005331422</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001443905934570873</v>
+        <v>0.02887811869141746</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001366286657139327</v>
+        <v>0.02732573314278654</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001290614628725676</v>
+        <v>0.02581229257451352</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001217199138433264</v>
+        <v>0.02434398276866528</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001146275092041341</v>
+        <v>0.02292550184082682</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001078014173545037</v>
+        <v>0.02156028347090074</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001012534573870906</v>
+        <v>0.02025069147741812</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0009499094567483364</v>
+        <v>0.01899818913496673</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008901743124922388</v>
+        <v>0.01780348624984478</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0008333333333333334</v>
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002173913043478261</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002122181051079939</v>
+        <v>0.04244362102159878</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002061264803224258</v>
+        <v>0.04122529606448516</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001993320395105952</v>
+        <v>0.03986640790211904</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001920182286218682</v>
+        <v>0.03840364572437364</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001843404479934556</v>
+        <v>0.03686808959869112</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001764296825192162</v>
+        <v>0.03528593650384324</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001683956991448237</v>
+        <v>0.03367913982896474</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001603298607719339</v>
+        <v>0.03206597215438678</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001523076002665711</v>
+        <v>0.03046152005331422</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001443905934570873</v>
+        <v>0.02887811869141746</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001366286657139327</v>
+        <v>0.02732573314278654</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001290614628725676</v>
+        <v>0.02581229257451352</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001217199138433264</v>
+        <v>0.02434398276866528</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001146275092041341</v>
+        <v>0.02292550184082682</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001078014173545037</v>
+        <v>0.02156028347090074</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001012534573870906</v>
+        <v>0.02025069147741812</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0009499094567483364</v>
+        <v>0.01899818913496673</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008901743124922388</v>
+        <v>0.01780348624984478</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0008333333333333334</v>
+        <v>0.01666666666666667</v>
       </c>
     </row>
   </sheetData>
